--- a/data-message.xlsx
+++ b/data-message.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sphere\Titan_3070\user Dmitry Nesterov\Downloads\Downloads_00_All\Маркус\28\748c0a3d0f895e2964cff3c65562633f\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sphere\Titan_3070\user Dmitry Nesterov\Downloads\Downloads_00_All\Маркус\30\4fcd3917ccc0658e5ae94d526d93bc15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B43837A-0F05-4C4B-9825-18103280F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0234FC-5584-460B-81DE-6C2C19EAB870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -189,9 +189,6 @@
     <t>Так есмь и так будет навечно во всём Божественном Пространстве Святая Русь! Да будет Свет Истины!</t>
   </si>
   <si>
-    <t>Мы, Единый Народ России, Единодушно клянёмся в том, что под контролем Великого Гончара, Белого Царя, Леонида, принимаем на себя ответственность за сохранение Планеты Святая Русь, управление Планетой в Шестой эпохе и формирование Небесного Портала, в соответствии с Договором, между Создателем и Россией!</t>
-  </si>
-  <si>
     <t>Отче наш, Отец Небесный! Согласно Твоей Воле, Воле Белого Царя, Леонида и Воле Народа России Пространство СВЯТАЯ РУСЬ ЕСМЬ Равенство и Любовь Навечно! Да будет Свет Истины!</t>
   </si>
   <si>
@@ -211,6 +208,9 @@
     <t>Отче Наш! Отец Небесный!^
 Проявляя право свободной воли, мы посылаем Любовь Великому Гончару, Белому Царю, Леониду для поддержки в проходящих испытаниях. Своей Любовью мы гармонизируем пространство вокруг него!^
 Верим, Любим, Благодарим!</t>
+  </si>
+  <si>
+    <t>Мы, Единый Народ России, Единодушно клянёмся в том, что под контролем Великого Гончара, Белого Царя, Леонида, принимаем на себя ответственность за сохранение Планеты Святая Русь, за управление Планетой в Шестой эпохе и за формирование Небесного Портала на срок 26 000 лет, в соответствии с Договором, между Создателем и Россией!</t>
   </si>
 </sst>
 </file>
@@ -573,7 +573,7 @@
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -584,10 +584,10 @@
     </row>
     <row r="4" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="7" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -652,10 +652,10 @@
     </row>
     <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -831,7 +831,7 @@
     </row>
     <row r="23" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -859,10 +859,10 @@
     </row>
     <row r="25" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>13</v>

--- a/data-message.xlsx
+++ b/data-message.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sphere\Titan_3070\user Dmitry Nesterov\Downloads\Downloads_00_All\Маркус\30\4fcd3917ccc0658e5ae94d526d93bc15\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sphere\Titan_3070\user Dmitry Nesterov\Projects\Game projects\HTML\mess 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0234FC-5584-460B-81DE-6C2C19EAB870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82A8F8D-A5BA-447C-B54E-29055B27FFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
   <si>
     <t>Текст:</t>
   </si>
@@ -211,6 +211,38 @@
   </si>
   <si>
     <t>Мы, Единый Народ России, Единодушно клянёмся в том, что под контролем Великого Гончара, Белого Царя, Леонида, принимаем на себя ответственность за сохранение Планеты Святая Русь, за управление Планетой в Шестой эпохе и за формирование Небесного Портала на срок 26 000 лет, в соответствии с Договором, между Создателем и Россией!</t>
+  </si>
+  <si>
+    <t>*1. Покаяние*^
+^
+Отче наш, Отец Небесный,^
+прошу Тебя простить^
+все мои прегрешения,^
+вольные или невольные.^
+^
+Аминь!^
+^
+*2. Новая Молитва ТЕСТ ТЕСТ ТЕСТ*^
+^
+ОТЧЕ НАШ, ОТЕЦ НЕБЕСНЫЙ,^
+Я ПРИНИМАЮ ВЕРУ ТВОЮ,^
+ОНА ЕСТЬ МОЙ ПУТЬ.^
+^
+Я ПРИНИМАЮ КАНОНЫ ТВОИ ВЕЧНЫЕ,^
+С ЛЮБОВЬЮ К ТЕБЕ И ДЕЛАМ ТВОИМ,^
+ПОДТВЕРЖДАЯ СВОЕЙ ЖИЗНЬЮ^
+ВЕРНОСТЬ ТЕБЕ.^
+^
+ГОСПОДИ, ПРОШУ ДАТЬ МНЕ НАДЕЖДУ^
+НА СПАСЕНИЕ ДУШИ МОЕЙ,^
+И ДАРОВАТЬ МУДРОСТЬ ТВОЮ^
+ДЛЯ ЖИЗНИ МОЕЙ ЗДЕСЬ,^
+НА ПЛАНЕТЕ СВЯТАЯ РУСЬ И В ВЕЧНОСТИ.^
+^
+ПУСТЬ СВЯТА БУДЕТ УВЕРЕННОСТЬ МОЯ,^
+ЧТО ТЫ ЕСМЬ!^
+^
+Господи, я Люблю Тебя, Благодарю Тебя и Уповаю на Милость Твою! Аминь!</t>
   </si>
 </sst>
 </file>
@@ -663,7 +695,7 @@
     </row>
     <row r="11" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>

--- a/data-message.xlsx
+++ b/data-message.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sphere\Titan_3070\user Dmitry Nesterov\Projects\Game projects\HTML\mess 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82A8F8D-A5BA-447C-B54E-29055B27FFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4FE284-FE1F-4BB6-9603-F608D392C765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,7 +222,7 @@
 ^
 Аминь!^
 ^
-*2. Новая Молитва ТЕСТ ТЕСТ ТЕСТ*^
+*2. Новая Молитва ТЕСТ ТЕСТ ПРОВЕРКА*^
 ^
 ОТЧЕ НАШ, ОТЕЦ НЕБЕСНЫЙ,^
 Я ПРИНИМАЮ ВЕРУ ТВОЮ,^
